--- a/backend/data/financials_by_company/1AE.AX.xlsx
+++ b/backend/data/financials_by_company/1AE.AX.xlsx
@@ -582,7 +582,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -591,91 +591,85 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2451776</v>
+        <v>-1913794</v>
       </c>
       <c r="E2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="F2" t="n">
-        <v>20738</v>
+        <v>502</v>
       </c>
       <c r="G2" t="n">
-        <v>-2451776</v>
+        <v>-1913794</v>
       </c>
       <c r="H2" t="n">
-        <v>-2472514</v>
+        <v>-1914296</v>
       </c>
       <c r="I2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="J2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="K2" t="n">
-        <v>179028669</v>
+        <v>104107017</v>
       </c>
       <c r="L2" t="n">
-        <v>179028669</v>
+        <v>104107017</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0127</v>
+        <v>-0.0184</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0127</v>
+        <v>-0.0184</v>
       </c>
       <c r="O2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="P2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="R2" t="n">
-        <v>-2357860</v>
+        <v>-1914296</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-2357860</v>
-      </c>
-      <c r="U2" t="n">
-        <v>114654</v>
-      </c>
-      <c r="V2" t="n">
-        <v>114654</v>
-      </c>
+        <v>-1914296</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-2472514</v>
+        <v>-1914296</v>
       </c>
       <c r="X2" t="n">
-        <v>2472514</v>
+        <v>1914296</v>
       </c>
       <c r="Y2" t="n">
-        <v>1520134</v>
+        <v>1162593</v>
       </c>
       <c r="Z2" t="n">
-        <v>20738</v>
+        <v>502</v>
       </c>
       <c r="AA2" t="n">
-        <v>20738</v>
+        <v>502</v>
       </c>
       <c r="AB2" t="n">
-        <v>20738</v>
+        <v>502</v>
       </c>
       <c r="AC2" t="n">
-        <v>931642</v>
+        <v>751201</v>
       </c>
       <c r="AD2" t="n">
-        <v>931642</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>362926</v>
-      </c>
+        <v>751201</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>568716</v>
+        <v>751201</v>
       </c>
     </row>
     <row r="3">
@@ -778,7 +772,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -787,85 +781,91 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-1913794</v>
+        <v>-2451776</v>
       </c>
       <c r="E4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="F4" t="n">
-        <v>502</v>
+        <v>20738</v>
       </c>
       <c r="G4" t="n">
-        <v>-1913794</v>
+        <v>-2451776</v>
       </c>
       <c r="H4" t="n">
-        <v>-1914296</v>
+        <v>-2472514</v>
       </c>
       <c r="I4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="J4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="K4" t="n">
-        <v>104107017</v>
+        <v>179028669</v>
       </c>
       <c r="L4" t="n">
-        <v>104107017</v>
+        <v>179028669</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0184</v>
+        <v>-0.0127</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0184</v>
+        <v>-0.0127</v>
       </c>
       <c r="O4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="P4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="R4" t="n">
-        <v>-1914296</v>
+        <v>-2357860</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1914296</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>-2357860</v>
+      </c>
+      <c r="U4" t="n">
+        <v>114654</v>
+      </c>
+      <c r="V4" t="n">
+        <v>114654</v>
+      </c>
       <c r="W4" t="n">
-        <v>-1914296</v>
+        <v>-2472514</v>
       </c>
       <c r="X4" t="n">
-        <v>1914296</v>
+        <v>2472514</v>
       </c>
       <c r="Y4" t="n">
-        <v>1162593</v>
+        <v>1520134</v>
       </c>
       <c r="Z4" t="n">
-        <v>502</v>
+        <v>20738</v>
       </c>
       <c r="AA4" t="n">
-        <v>502</v>
+        <v>20738</v>
       </c>
       <c r="AB4" t="n">
-        <v>502</v>
+        <v>20738</v>
       </c>
       <c r="AC4" t="n">
-        <v>751201</v>
+        <v>931642</v>
       </c>
       <c r="AD4" t="n">
-        <v>751201</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>931642</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>362926</v>
+      </c>
       <c r="AF4" t="n">
-        <v>751201</v>
+        <v>568716</v>
       </c>
     </row>
   </sheetData>
@@ -1061,110 +1061,108 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="n">
-        <v>179063737</v>
+        <v>142610990</v>
       </c>
       <c r="C2" t="n">
-        <v>179063737</v>
+        <v>142610990</v>
       </c>
       <c r="D2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="E2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="F2" t="n">
-        <v>1513131</v>
+        <v>7091437</v>
       </c>
       <c r="G2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="H2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="I2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="J2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="K2" t="n">
-        <v>1908706</v>
+        <v>7093813</v>
       </c>
       <c r="L2" t="n">
-        <v>784552</v>
+        <v>482611</v>
       </c>
       <c r="M2" t="n">
-        <v>784552</v>
+        <v>482611</v>
       </c>
       <c r="N2" t="n">
-        <v>-12904887</v>
+        <v>-4884877</v>
       </c>
       <c r="O2" t="n">
-        <v>14029041</v>
+        <v>11496079</v>
       </c>
       <c r="P2" t="n">
-        <v>14029041</v>
+        <v>11496079</v>
       </c>
       <c r="Q2" t="n">
-        <v>366289</v>
+        <v>292041</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>366289</v>
+        <v>292041</v>
       </c>
       <c r="T2" t="n">
-        <v>366289</v>
+        <v>292041</v>
       </c>
       <c r="U2" t="n">
-        <v>366289</v>
+        <v>292041</v>
       </c>
       <c r="V2" t="n">
-        <v>156288</v>
+        <v>94438</v>
       </c>
       <c r="W2" t="n">
-        <v>210001</v>
+        <v>197603</v>
       </c>
       <c r="X2" t="n">
-        <v>2274995</v>
+        <v>7385854</v>
       </c>
       <c r="Y2" t="n">
-        <v>395575</v>
+        <v>2376</v>
       </c>
       <c r="Z2" t="n">
-        <v>395575</v>
+        <v>2376</v>
       </c>
       <c r="AA2" t="n">
-        <v>395575</v>
+        <v>2376</v>
       </c>
       <c r="AB2" t="n">
-        <v>395575</v>
+        <v>2376</v>
       </c>
       <c r="AC2" t="n">
-        <v>1879420</v>
+        <v>7383478</v>
       </c>
       <c r="AD2" t="n">
-        <v>284249</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>284249</v>
-      </c>
+        <v>66199</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>66199</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>1595171</v>
+        <v>7317279</v>
       </c>
       <c r="AH2" t="n">
-        <v>1595171</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>550000</v>
-      </c>
+        <v>7317279</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>1045171</v>
+        <v>7317279</v>
       </c>
     </row>
     <row r="3">
@@ -1275,108 +1273,110 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>142610990</v>
+        <v>179063737</v>
       </c>
       <c r="C4" t="n">
-        <v>142610990</v>
+        <v>179063737</v>
       </c>
       <c r="D4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="E4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="F4" t="n">
-        <v>7091437</v>
+        <v>1513131</v>
       </c>
       <c r="G4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="H4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="I4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="J4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="K4" t="n">
-        <v>7093813</v>
+        <v>1908706</v>
       </c>
       <c r="L4" t="n">
-        <v>482611</v>
+        <v>784552</v>
       </c>
       <c r="M4" t="n">
-        <v>482611</v>
+        <v>784552</v>
       </c>
       <c r="N4" t="n">
-        <v>-4884877</v>
+        <v>-12904887</v>
       </c>
       <c r="O4" t="n">
-        <v>11496079</v>
+        <v>14029041</v>
       </c>
       <c r="P4" t="n">
-        <v>11496079</v>
+        <v>14029041</v>
       </c>
       <c r="Q4" t="n">
-        <v>292041</v>
+        <v>366289</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>292041</v>
+        <v>366289</v>
       </c>
       <c r="T4" t="n">
-        <v>292041</v>
+        <v>366289</v>
       </c>
       <c r="U4" t="n">
-        <v>292041</v>
+        <v>366289</v>
       </c>
       <c r="V4" t="n">
-        <v>94438</v>
+        <v>156288</v>
       </c>
       <c r="W4" t="n">
-        <v>197603</v>
+        <v>210001</v>
       </c>
       <c r="X4" t="n">
-        <v>7385854</v>
+        <v>2274995</v>
       </c>
       <c r="Y4" t="n">
-        <v>2376</v>
+        <v>395575</v>
       </c>
       <c r="Z4" t="n">
-        <v>2376</v>
+        <v>395575</v>
       </c>
       <c r="AA4" t="n">
-        <v>2376</v>
+        <v>395575</v>
       </c>
       <c r="AB4" t="n">
-        <v>2376</v>
+        <v>395575</v>
       </c>
       <c r="AC4" t="n">
-        <v>7383478</v>
+        <v>1879420</v>
       </c>
       <c r="AD4" t="n">
-        <v>66199</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>66199</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>284249</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>284249</v>
+      </c>
       <c r="AG4" t="n">
-        <v>7317279</v>
+        <v>1595171</v>
       </c>
       <c r="AH4" t="n">
-        <v>7317279</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>1595171</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>550000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>7317279</v>
+        <v>1045171</v>
       </c>
     </row>
   </sheetData>
@@ -1537,78 +1537,86 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44742</v>
       </c>
       <c r="B2" t="n">
-        <v>-2015473</v>
+        <v>-1175824</v>
       </c>
       <c r="C2" t="n">
-        <v>-14515</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>-392099</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10000</v>
+      </c>
       <c r="E2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>8801500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-2878</v>
+      </c>
       <c r="G2" t="n">
-        <v>1595171</v>
+        <v>7317279</v>
       </c>
       <c r="H2" t="n">
-        <v>3553657</v>
+        <v>79059</v>
       </c>
       <c r="I2" t="n">
-        <v>11502</v>
+        <v>-5357</v>
       </c>
       <c r="J2" t="n">
-        <v>-1969988</v>
+        <v>7243577</v>
       </c>
       <c r="K2" t="n">
-        <v>45485</v>
+        <v>8419401</v>
       </c>
       <c r="L2" t="n">
-        <v>45485</v>
+        <v>8419401</v>
       </c>
       <c r="M2" t="n">
-        <v>45485</v>
+        <v>8409401</v>
       </c>
       <c r="N2" t="n">
-        <v>-14515</v>
+        <v>-392099</v>
       </c>
       <c r="O2" t="n">
-        <v>60000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>8801500</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10000</v>
+      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-2878</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>-2878</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-2878</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-2878</v>
+      </c>
       <c r="W2" t="n">
-        <v>-2015473</v>
-      </c>
-      <c r="X2" t="n">
-        <v>14888</v>
-      </c>
+        <v>-1172946</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-2130361</v>
+        <v>-1172946</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1088657</v>
+        <v>-415154</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1041704</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>100000</v>
-      </c>
+        <v>-757792</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1691,86 +1699,78 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>-1175824</v>
+        <v>-2015473</v>
       </c>
       <c r="C4" t="n">
-        <v>-392099</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10000</v>
-      </c>
+        <v>-14515</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>8801500</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-2878</v>
-      </c>
+        <v>60000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>7317279</v>
+        <v>1595171</v>
       </c>
       <c r="H4" t="n">
-        <v>79059</v>
+        <v>3553657</v>
       </c>
       <c r="I4" t="n">
-        <v>-5357</v>
+        <v>11502</v>
       </c>
       <c r="J4" t="n">
-        <v>7243577</v>
+        <v>-1969988</v>
       </c>
       <c r="K4" t="n">
-        <v>8419401</v>
+        <v>45485</v>
       </c>
       <c r="L4" t="n">
-        <v>8419401</v>
+        <v>45485</v>
       </c>
       <c r="M4" t="n">
-        <v>8409401</v>
+        <v>45485</v>
       </c>
       <c r="N4" t="n">
-        <v>-392099</v>
+        <v>-14515</v>
       </c>
       <c r="O4" t="n">
-        <v>8801500</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10000</v>
-      </c>
+        <v>60000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-2878</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-2878</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-2878</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-2878</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-1172946</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>-2015473</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14888</v>
+      </c>
       <c r="Y4" t="n">
-        <v>-1172946</v>
+        <v>-2130361</v>
       </c>
       <c r="Z4" t="n">
-        <v>-415154</v>
+        <v>-1088657</v>
       </c>
       <c r="AA4" t="n">
-        <v>-757792</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+        <v>-1041704</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>100000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2274,172 +2274,172 @@
       </c>
       <c r="CT1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EB1" t="inlineStr">
@@ -2549,61 +2549,61 @@
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="W2" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="X2" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.906</v>
+        <v>0.864</v>
       </c>
       <c r="AF2" t="n">
-        <v>51469</v>
+        <v>183773</v>
       </c>
       <c r="AG2" t="n">
-        <v>51469</v>
+        <v>183773</v>
       </c>
       <c r="AH2" t="n">
-        <v>353839</v>
+        <v>272541</v>
       </c>
       <c r="AI2" t="n">
-        <v>240385</v>
+        <v>215410</v>
       </c>
       <c r="AJ2" t="n">
-        <v>240385</v>
+        <v>215410</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="AM2" t="n">
-        <v>10564761</v>
+        <v>10206633</v>
       </c>
       <c r="AN2" t="n">
-        <v>10027569</v>
+        <v>10206633</v>
       </c>
       <c r="AO2" t="n">
         <v>0.046</v>
@@ -2618,13 +2618,13 @@
         <v>0.033</v>
       </c>
       <c r="AS2" t="n">
-        <v>897.67706</v>
+        <v>867.24725</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.06571</v>
+        <v>0.06575</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.08676250000000001</v>
+        <v>0.0858925</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -2641,19 +2641,19 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8566728</v>
+        <v>8745792</v>
       </c>
       <c r="BA2" t="n">
         <v>69.87255</v>
       </c>
       <c r="BB2" t="n">
-        <v>101484373</v>
+        <v>101088642</v>
       </c>
       <c r="BC2" t="n">
         <v>179063737</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3236</v>
+        <v>0.32582</v>
       </c>
       <c r="BE2" t="n">
         <v>0.08104999</v>
@@ -2665,7 +2665,7 @@
         <v>0.013</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.5384617</v>
+        <v>4.3846154</v>
       </c>
       <c r="BI2" t="n">
         <v>1751241600</v>
@@ -2683,16 +2683,16 @@
         <v>-0</v>
       </c>
       <c r="BN2" t="n">
-        <v>727.9059999999999</v>
+        <v>743.121</v>
       </c>
       <c r="BO2" t="n">
-        <v>-13.384</v>
+        <v>-13.664</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.22222221</v>
+        <v>0.0363636</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -2798,129 +2798,129 @@
       </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>AURORAENER FPO [1AE]</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>0.057 - 0.064</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>272541</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.23913044</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>0.046 - 0.155</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.098000005</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.6322581</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>3.6363602</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.008750002999999999</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.13307989</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.028892498</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.33637977</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1652832000000</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Aurora Energy Metals Limited</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CU2" t="n">
-        <v>1780445652</v>
-      </c>
-      <c r="CV2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>1782105225</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>ASX</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>finmb_1776422441</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Australia/Sydney</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>AEST</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DY2" t="n">
         <v>36000000</v>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>au_market</t>
         </is>
       </c>
-      <c r="DB2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>5.35714</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>AURORAENER FPO [1AE]</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.0029999986</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>0.059 - 0.059</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>353839</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.2826087</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>0.046 - 0.155</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.096</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.61935484</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-22.222221</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.0067100003</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.10211536</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.027762502</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.31998274</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1652832000000</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Aurora Energy Metals Limited</t>
-        </is>
       </c>
       <c r="EB2" t="inlineStr"/>
     </row>
